--- a/虚拟棋战_棋子与羁绊_20260919.xlsx
+++ b/虚拟棋战_棋子与羁绊_20260919.xlsx
@@ -2198,8 +2198,8 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2人：全队每秒回复 1 生命
-4人：全队每秒回复 2 生命（现有成员 5 人）</t>
+          <t>2人：每 5 秒为生命比例最低的队友回复 4% 最大生命（急救）
+4人：每 5 秒为生命比例最低的两名队友各回复 6% 最大生命（急救）（现有成员 5 人）</t>
         </is>
       </c>
     </row>
